--- a/src/xlsx/enriched_data.xlsx
+++ b/src/xlsx/enriched_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ101"/>
+  <dimension ref="A1:AR101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,20 +591,60 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>stadium_name</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>stadium_capacity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>world_cup_titles</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>continental_trophies</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>contract_tier</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>rep_stars</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>main_sponsor</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>sponsor_tier</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>wage_tier</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>market_value_tier</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>is_intercontinental</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>star_rating_index</t>
         </is>
@@ -735,18 +775,50 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0.9716</v>
       </c>
     </row>
@@ -875,18 +947,50 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
         <v>0.8512</v>
       </c>
     </row>
@@ -1015,18 +1119,50 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
         <v>0.9695</v>
       </c>
     </row>
@@ -1155,18 +1291,50 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>Cívitas Metropolitano</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>68456</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
         <v>0.8747</v>
       </c>
     </row>
@@ -1295,18 +1463,50 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
         <v>0.9103</v>
       </c>
     </row>
@@ -1435,18 +1635,50 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
         <v>0.9103</v>
       </c>
     </row>
@@ -1575,18 +1807,50 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
         <v>0.831</v>
       </c>
     </row>
@@ -1715,18 +1979,50 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
         <v>0.8609</v>
       </c>
     </row>
@@ -1855,18 +2151,50 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
         <v>0.7671</v>
       </c>
     </row>
@@ -1995,18 +2323,50 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
         <v>0.868</v>
       </c>
     </row>
@@ -2135,18 +2495,50 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
         <v>0.8898</v>
       </c>
     </row>
@@ -2275,18 +2667,50 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
         <v>0.8159</v>
       </c>
     </row>
@@ -2415,18 +2839,50 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
         <v>0.8599</v>
       </c>
     </row>
@@ -2555,18 +3011,50 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
         <v>0.7887999999999999</v>
       </c>
     </row>
@@ -2695,18 +3183,50 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>Old Trafford</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>74310</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
         <v>0.7832</v>
       </c>
     </row>
@@ -2835,18 +3355,50 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>Stamford Bridge</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>40834</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
         <v>0.8116</v>
       </c>
     </row>
@@ -2975,18 +3527,50 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -3115,18 +3699,50 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
         <v>0.7945</v>
       </c>
     </row>
@@ -3255,18 +3871,50 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
         <v>0.7135</v>
       </c>
     </row>
@@ -3395,18 +4043,50 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
         <v>0.7746</v>
       </c>
     </row>
@@ -3535,18 +4215,50 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
         <v>0.8073</v>
       </c>
     </row>
@@ -3675,18 +4387,50 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AP23" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
         <v>0.7803</v>
       </c>
     </row>
@@ -3815,18 +4559,50 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
         <v>0.8201000000000001</v>
       </c>
     </row>
@@ -3955,18 +4731,50 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
         <v>0.8263</v>
       </c>
     </row>
@@ -4095,18 +4903,50 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>Old Trafford</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>74310</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AP26" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
         <v>0.8149</v>
       </c>
     </row>
@@ -4235,18 +5075,50 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
         <v>0.7637</v>
       </c>
     </row>
@@ -4375,18 +5247,50 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AP28" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
         <v>0.8163</v>
       </c>
     </row>
@@ -4515,18 +5419,50 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AP29" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
         <v>0.8021</v>
       </c>
     </row>
@@ -4655,18 +5591,50 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AP30" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
         <v>0.7452</v>
       </c>
     </row>
@@ -4795,18 +5763,50 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AP31" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
         <v>0.7168</v>
       </c>
     </row>
@@ -4935,18 +5935,50 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AP32" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
         <v>0.6827</v>
       </c>
     </row>
@@ -5075,18 +6107,50 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr">
+      <c r="AP33" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
         <v>0.6997</v>
       </c>
     </row>
@@ -5215,18 +6279,50 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr">
+      <c r="AP34" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
         <v>0.7111</v>
       </c>
     </row>
@@ -5355,18 +6451,50 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH35" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
         <v>0.7111</v>
       </c>
     </row>
@@ -5495,18 +6623,50 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH36" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr">
+      <c r="AP36" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="n">
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
         <v>0.7423999999999999</v>
       </c>
     </row>
@@ -5635,18 +6795,50 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH37" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH37" t="inlineStr">
+      <c r="AP37" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
         <v>0.6883</v>
       </c>
     </row>
@@ -5775,18 +6967,50 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH38" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH38" t="inlineStr">
+      <c r="AP38" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
         <v>0.7708</v>
       </c>
     </row>
@@ -5915,18 +7139,50 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
+          <t>Signal Iduna Park</t>
+        </is>
+      </c>
+      <c r="AH39" t="n">
+        <v>81365</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AP39" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
         <v>0.768</v>
       </c>
     </row>
@@ -6055,18 +7311,50 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
+          <t>Emirates Stadium</t>
+        </is>
+      </c>
+      <c r="AH40" t="n">
+        <v>60704</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH40" t="inlineStr">
+      <c r="AP40" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="n">
+      <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
         <v>0.7708</v>
       </c>
     </row>
@@ -6195,18 +7483,50 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH41" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AP41" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ41" t="n">
+      <c r="AQ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" t="n">
         <v>0.785</v>
       </c>
     </row>
@@ -6335,18 +7655,50 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH42" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH42" t="inlineStr">
+      <c r="AP42" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
         <v>0.7541</v>
       </c>
     </row>
@@ -6475,18 +7827,50 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH43" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH43" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
         <v>0.7755</v>
       </c>
     </row>
@@ -6615,18 +7999,50 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH44" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH44" t="inlineStr">
+      <c r="AP44" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="n">
+      <c r="AQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" t="n">
         <v>0.7456</v>
       </c>
     </row>
@@ -6755,18 +8171,50 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AP45" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ45" t="n">
+      <c r="AQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" t="n">
         <v>0.7641</v>
       </c>
     </row>
@@ -6895,18 +8343,50 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH46" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ46" t="n">
+      <c r="AQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR46" t="n">
         <v>0.6489</v>
       </c>
     </row>
@@ -7035,18 +8515,50 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH47" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH47" t="inlineStr">
+      <c r="AP47" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="n">
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
         <v>0.6461</v>
       </c>
     </row>
@@ -7175,18 +8687,50 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH48" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AP48" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
         <v>0.7214</v>
       </c>
     </row>
@@ -7315,18 +8859,50 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH49" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr">
+      <c r="AP49" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
         <v>0.6859</v>
       </c>
     </row>
@@ -7455,18 +9031,50 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH50" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH50" t="inlineStr">
+      <c r="AP50" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
         <v>0.7072000000000001</v>
       </c>
     </row>
@@ -7595,18 +9203,50 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
+          <t>Signal Iduna Park</t>
+        </is>
+      </c>
+      <c r="AH51" t="n">
+        <v>81365</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AP51" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -7735,18 +9375,50 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH52" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AP52" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -7875,18 +9547,50 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH53" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH53" t="inlineStr">
+      <c r="AP53" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
         <v>0.7072000000000001</v>
       </c>
     </row>
@@ -8015,18 +9719,50 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH54" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH54" t="inlineStr">
+      <c r="AP54" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
         <v>0.7356</v>
       </c>
     </row>
@@ -8155,18 +9891,50 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH55" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH55" t="inlineStr">
+      <c r="AP55" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
         <v>0.6802</v>
       </c>
     </row>
@@ -8295,18 +10063,50 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH56" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH56" t="inlineStr">
+      <c r="AP56" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
         <v>0.7413</v>
       </c>
     </row>
@@ -8435,18 +10235,50 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH57" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
         <v>0.7517</v>
       </c>
     </row>
@@ -8575,18 +10407,50 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH58" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AP58" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ58" t="n">
+      <c r="AQ58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR58" t="n">
         <v>0.7247</v>
       </c>
     </row>
@@ -8715,18 +10579,50 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH59" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH59" t="inlineStr">
+      <c r="AP59" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="n">
+      <c r="AQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR59" t="n">
         <v>0.7261</v>
       </c>
     </row>
@@ -8855,18 +10751,50 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH60" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AP60" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
         <v>0.7332</v>
       </c>
     </row>
@@ -8995,18 +10923,50 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH61" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH61" t="inlineStr">
+      <c r="AP61" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="n">
         <v>0.7205</v>
       </c>
     </row>
@@ -9135,18 +11095,50 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH62" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH62" t="inlineStr">
+      <c r="AP62" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
+      <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="n">
         <v>0.6849</v>
       </c>
     </row>
@@ -9275,18 +11267,50 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH63" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH63" t="inlineStr">
+      <c r="AP63" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -9415,18 +11439,50 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH64" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH64" t="inlineStr">
+      <c r="AP64" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
         <v>0.7233000000000001</v>
       </c>
     </row>
@@ -9555,18 +11611,50 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH65" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH65" t="inlineStr">
+      <c r="AP65" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ65" t="n">
+      <c r="AQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR65" t="n">
         <v>0.7261</v>
       </c>
     </row>
@@ -9695,18 +11783,50 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH66" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AP66" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
         <v>0.6863</v>
       </c>
     </row>
@@ -9835,18 +11955,50 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH67" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH67" t="inlineStr">
+      <c r="AP67" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="n">
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
         <v>0.6991000000000001</v>
       </c>
     </row>
@@ -9975,18 +12127,50 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
+          <t>Parc des Princes</t>
+        </is>
+      </c>
+      <c r="AH68" t="n">
+        <v>47929</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH68" t="inlineStr">
+      <c r="AP68" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ68" t="n">
+      <c r="AQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR68" t="n">
         <v>0.6892</v>
       </c>
     </row>
@@ -10115,18 +12299,50 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH69" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH69" t="inlineStr">
+      <c r="AP69" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="n">
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
         <v>0.6593</v>
       </c>
     </row>
@@ -10255,18 +12471,50 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH70" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH70" t="inlineStr">
+      <c r="AP70" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ70" t="n">
+      <c r="AQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR70" t="n">
         <v>0.7105</v>
       </c>
     </row>
@@ -10395,18 +12643,50 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH71" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH71" t="inlineStr">
+      <c r="AP71" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
+      <c r="AQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="n">
         <v>0.6949</v>
       </c>
     </row>
@@ -10535,18 +12815,50 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH72" t="inlineStr">
+      <c r="AP72" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
         <v>0.702</v>
       </c>
     </row>
@@ -10675,18 +12987,50 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH73" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH73" t="inlineStr">
+      <c r="AP73" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
+      <c r="AQ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR73" t="n">
         <v>0.7048</v>
       </c>
     </row>
@@ -10815,18 +13159,50 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
+          <t>Emirates Stadium</t>
+        </is>
+      </c>
+      <c r="AH74" t="n">
+        <v>60704</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH74" t="inlineStr">
+      <c r="AP74" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
+      <c r="AQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR74" t="n">
         <v>0.7091</v>
       </c>
     </row>
@@ -10955,18 +13331,50 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH75" t="inlineStr">
+      <c r="AP75" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ75" t="n">
+      <c r="AQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR75" t="n">
         <v>0.7052</v>
       </c>
     </row>
@@ -11095,18 +13503,50 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH76" t="inlineStr">
+      <c r="AP76" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="n">
+      <c r="AQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR76" t="n">
         <v>0.681</v>
       </c>
     </row>
@@ -11235,18 +13675,50 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH77" t="inlineStr">
+      <c r="AP77" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="n">
+      <c r="AQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR77" t="n">
         <v>0.7109</v>
       </c>
     </row>
@@ -11375,18 +13847,50 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH78" t="inlineStr">
+      <c r="AP78" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ78" t="n">
+      <c r="AQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="n">
         <v>0.6909999999999999</v>
       </c>
     </row>
@@ -11515,18 +14019,50 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH79" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr">
+      <c r="AP79" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
+      <c r="AQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="n">
         <v>0.6952</v>
       </c>
     </row>
@@ -11655,18 +14191,50 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH80" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH80" t="inlineStr">
+      <c r="AP80" t="inlineStr">
         <is>
           <t>Superstar (&gt;50M)</t>
         </is>
       </c>
-      <c r="AI80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ80" t="n">
+      <c r="AQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="n">
         <v>0.7066</v>
       </c>
     </row>
@@ -11795,18 +14363,50 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
+          <t>Etihad Stadium</t>
+        </is>
+      </c>
+      <c r="AH81" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH81" t="inlineStr">
+      <c r="AP81" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="n">
+      <c r="AQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR81" t="n">
         <v>0.6967</v>
       </c>
     </row>
@@ -11935,18 +14535,50 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
+          <t>Cívitas Metropolitano</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>68456</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH82" t="inlineStr">
+      <c r="AP82" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="n">
+      <c r="AQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="n">
         <v>0.7038</v>
       </c>
     </row>
@@ -12075,18 +14707,50 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH83" t="inlineStr">
+      <c r="AP83" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ83" t="n">
+      <c r="AQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR83" t="n">
         <v>0.6909999999999999</v>
       </c>
     </row>
@@ -12215,18 +14879,50 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
+        <v>53394</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH84" t="inlineStr">
+      <c r="AP84" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="n">
+      <c r="AQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="n">
         <v>0.6867</v>
       </c>
     </row>
@@ -12355,18 +15051,50 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
+          <t>Cívitas Metropolitano</t>
+        </is>
+      </c>
+      <c r="AH85" t="n">
+        <v>68456</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH85" t="inlineStr">
+      <c r="AP85" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ85" t="n">
+      <c r="AQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR85" t="n">
         <v>0.6909999999999999</v>
       </c>
     </row>
@@ -12495,18 +15223,50 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH86" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH86" t="inlineStr">
+      <c r="AP86" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ86" t="n">
+      <c r="AQ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR86" t="n">
         <v>0.6909999999999999</v>
       </c>
     </row>
@@ -12635,18 +15395,50 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
           <t>Medio (5k-25k)</t>
         </is>
       </c>
-      <c r="AH87" t="inlineStr">
+      <c r="AP87" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="n">
+      <c r="AQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR87" t="n">
         <v>0.7023</v>
       </c>
     </row>
@@ -12775,18 +15567,50 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH88" t="inlineStr">
+      <c r="AP88" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ88" t="n">
+      <c r="AQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR88" t="n">
         <v>0.6583</v>
       </c>
     </row>
@@ -12915,18 +15739,50 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH89" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH89" t="inlineStr">
+      <c r="AP89" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ89" t="n">
+      <c r="AQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR89" t="n">
         <v>0.6512</v>
       </c>
     </row>
@@ -13055,18 +15911,50 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
+          <t>Signal Iduna Park</t>
+        </is>
+      </c>
+      <c r="AH90" t="n">
+        <v>81365</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH90" t="inlineStr">
+      <c r="AP90" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ90" t="n">
+      <c r="AQ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR90" t="n">
         <v>0.654</v>
       </c>
     </row>
@@ -13195,18 +16083,50 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH91" t="inlineStr">
+      <c r="AP91" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ91" t="n">
+      <c r="AQ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR91" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -13335,18 +16255,50 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH92" t="inlineStr">
+      <c r="AP92" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI92" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ92" t="n">
+      <c r="AQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR92" t="n">
         <v>0.6696</v>
       </c>
     </row>
@@ -13475,18 +16427,50 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
+          <t>Camp Nou</t>
+        </is>
+      </c>
+      <c r="AH93" t="n">
+        <v>99354</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH93" t="inlineStr">
+      <c r="AP93" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ93" t="n">
+      <c r="AQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR93" t="n">
         <v>0.6512</v>
       </c>
     </row>
@@ -13615,18 +16599,50 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AH94" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH94" t="inlineStr">
+      <c r="AP94" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ94" t="n">
+      <c r="AQ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR94" t="n">
         <v>0.6711</v>
       </c>
     </row>
@@ -13755,18 +16771,50 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH95" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH95" t="inlineStr">
+      <c r="AP95" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ95" t="n">
+      <c r="AQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR95" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -13895,18 +16943,50 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
+          <t>Santiago Bernabéu</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>81044</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH96" t="inlineStr">
+      <c r="AP96" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ96" t="n">
+      <c r="AQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR96" t="n">
         <v>0.6711</v>
       </c>
     </row>
@@ -14035,18 +17115,50 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH97" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AP97" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ97" t="n">
+      <c r="AQ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR97" t="n">
         <v>0.6909999999999999</v>
       </c>
     </row>
@@ -14175,18 +17287,50 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH98" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL98" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
           <t>Medio (5k-25k)</t>
         </is>
       </c>
-      <c r="AH98" t="inlineStr">
+      <c r="AP98" t="inlineStr">
         <is>
           <t>Profesional (2M-15M)</t>
         </is>
       </c>
-      <c r="AI98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ98" t="n">
+      <c r="AQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR98" t="n">
         <v>0.6028</v>
       </c>
     </row>
@@ -14315,18 +17459,50 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
+          <t>Municipal Arena</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Regional Sponsor</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
           <t>Alto (25k-100k)</t>
         </is>
       </c>
-      <c r="AH99" t="inlineStr">
+      <c r="AP99" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ99" t="n">
+      <c r="AQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR99" t="n">
         <v>0.6597</v>
       </c>
     </row>
@@ -14455,18 +17631,50 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH100" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH100" t="inlineStr">
+      <c r="AP100" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ100" t="n">
+      <c r="AQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR100" t="n">
         <v>0.6611</v>
       </c>
     </row>
@@ -14595,18 +17803,50 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
+          <t>Allianz Stadium</t>
+        </is>
+      </c>
+      <c r="AH101" t="n">
+        <v>41507</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="AL101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Global Brand Sponsor</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
           <t>Elite (&gt;100k)</t>
         </is>
       </c>
-      <c r="AH101" t="inlineStr">
+      <c r="AP101" t="inlineStr">
         <is>
           <t>Estelar (15M-50M)</t>
         </is>
       </c>
-      <c r="AI101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ101" t="n">
+      <c r="AQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR101" t="n">
         <v>0.6341</v>
       </c>
     </row>
